--- a/diseases/d101/2026-2029.xlsx
+++ b/diseases/d101/2026-2029.xlsx
@@ -8171,6 +8171,151 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>45</v>
+      </c>
+      <c r="O49" t="n">
+        <v>45</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.01289267159746223</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8204,7 +8349,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8432,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -8297,7 +8442,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -8349,7 +8494,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d101/2026-2029.xlsx
+++ b/diseases/d101/2026-2029.xlsx
@@ -6894,12 +6894,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -6933,81 +6933,92 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>28</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.00802210677175428</v>
+        <v>0</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CANDIDA_AURIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CANDIDA_AURIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7034,17 +7045,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7069,7 +7080,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -7078,81 +7089,170 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>45</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.01289267159746223</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CANDIDA_AURIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CANDIDA_AURIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary Candida auris notifications.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CANDIDA_AURIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7314,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -7223,13 +7323,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O42" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R42" t="n">
-        <v>0.00974112965141591</v>
+        <v>0.00802210677175428</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -7359,7 +7459,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -7368,13 +7468,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O43" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01002763346469285</v>
+        <v>0.01289267159746223</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -7504,22 +7604,22 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O44" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="R44" t="n">
-        <v>0.00802210677175428</v>
+        <v>0.00974112965141591</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7649,22 +7749,22 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="O45" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="R45" t="n">
-        <v>0.01461169447712387</v>
+        <v>0.01002763346469285</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -7794,7 +7894,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -7803,13 +7903,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O46" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R46" t="n">
-        <v>0.007735602958477341</v>
+        <v>0.00802210677175428</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7939,7 +8039,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7948,13 +8048,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="O47" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="R47" t="n">
-        <v>0.02292030506215508</v>
+        <v>0.01461169447712387</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -8084,7 +8184,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -8093,13 +8193,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="O48" t="n">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="R48" t="n">
-        <v>0.02349331268870896</v>
+        <v>0.007735602958477341</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -8229,22 +8329,22 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="O49" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01289267159746223</v>
+        <v>0.02292030506215508</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8311,6 +8411,296 @@
         </is>
       </c>
       <c r="BC49" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>82</v>
+      </c>
+      <c r="O50" t="n">
+        <v>82</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.02349331268870896</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>45</v>
+      </c>
+      <c r="O51" t="n">
+        <v>45</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.01289267159746223</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -8432,7 +8822,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -8442,7 +8832,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -8462,7 +8852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d101/2026-2029.xlsx
+++ b/diseases/d101/2026-2029.xlsx
@@ -8706,6 +8706,151 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>63</v>
+      </c>
+      <c r="O52" t="n">
+        <v>63</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.01804974023644713</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8739,7 +8884,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8967,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -8832,7 +8977,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -8884,7 +9029,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1429</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d101/2026-2029.xlsx
+++ b/diseases/d101/2026-2029.xlsx
@@ -8851,6 +8851,151 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>60</v>
+      </c>
+      <c r="O53" t="n">
+        <v>60</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.01719022879661631</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8884,7 +9029,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -8967,7 +9112,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -8977,7 +9122,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -9029,7 +9174,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1492</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d101/2026-2029.xlsx
+++ b/diseases/d101/2026-2029.xlsx
@@ -8996,6 +8996,151 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>35</v>
+      </c>
+      <c r="O54" t="n">
+        <v>35</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.01002763346469285</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9029,7 +9174,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9257,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -9122,7 +9267,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -9174,7 +9319,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1552</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d101/2026-2029.xlsx
+++ b/diseases/d101/2026-2029.xlsx
@@ -1166,6 +1166,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1314,6 +1319,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1462,6 +1472,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1610,6 +1625,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1758,6 +1778,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2296,6 +2321,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2444,6 +2474,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2592,6 +2627,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2740,6 +2780,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3278,6 +3323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3426,6 +3476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3574,6 +3629,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3722,6 +3782,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4260,6 +4325,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4408,6 +4478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4556,6 +4631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4704,6 +4784,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5242,6 +5327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5390,6 +5480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5538,6 +5633,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5686,6 +5786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5831,6 +5936,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6366,6 +6476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6511,6 +6626,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6656,6 +6776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6801,6 +6926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7336,6 +7466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7481,6 +7616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7626,6 +7766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7771,6 +7916,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7864,12 +8014,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7903,81 +8053,92 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>28</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0.00802210677175428</v>
+        <v>0</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CANDIDA_AURIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CANDIDA_AURIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8004,17 +8165,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8039,7 +8200,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -8048,81 +8209,170 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>51</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.01461169447712387</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CANDIDA_AURIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CANDIDA_AURIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary Candida auris notifications.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CANDIDA_AURIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8434,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -8193,17 +8443,22 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O48" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R48" t="n">
-        <v>0.007735602958477341</v>
+        <v>0.00802210677175428</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -8329,7 +8584,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -8338,17 +8593,22 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="O49" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="R49" t="n">
-        <v>0.02292030506215508</v>
+        <v>0.01461169447712387</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -8474,7 +8734,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -8483,17 +8743,22 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="O50" t="n">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="R50" t="n">
-        <v>0.02349331268870896</v>
+        <v>0.007735602958477341</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8619,26 +8884,31 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="O51" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01289267159746223</v>
+        <v>0.02292030506215508</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8764,26 +9034,31 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="O52" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="R52" t="n">
-        <v>0.01804974023644713</v>
+        <v>0.02349331268870896</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8909,7 +9184,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -8918,17 +9193,22 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="O53" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="R53" t="n">
-        <v>0.01719022879661631</v>
+        <v>0.01289267159746223</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -9054,7 +9334,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -9063,17 +9343,22 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="O54" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="R54" t="n">
-        <v>0.01002763346469285</v>
+        <v>0.01804974023644713</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -9136,6 +9421,456 @@
         </is>
       </c>
       <c r="BC54" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>60</v>
+      </c>
+      <c r="O55" t="n">
+        <v>60</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.01719022879661631</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>35</v>
+      </c>
+      <c r="O56" t="n">
+        <v>35</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.01002763346469285</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>50</v>
+      </c>
+      <c r="O57" t="n">
+        <v>50</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.01432519066384693</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -9174,7 +9909,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9992,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -9267,7 +10002,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -9287,7 +10022,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -9319,7 +10054,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1587</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d101/2026-2029.xlsx
+++ b/diseases/d101/2026-2029.xlsx
@@ -1155,9 +1155,6 @@
       <c r="O4" t="n">
         <v>13</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.003724549572600201</v>
       </c>
@@ -1308,9 +1305,6 @@
       <c r="O5" t="n">
         <v>32</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.009168122024862033</v>
       </c>
@@ -1461,9 +1455,6 @@
       <c r="O6" t="n">
         <v>49</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.01403868685056999</v>
       </c>
@@ -1614,9 +1605,6 @@
       <c r="O7" t="n">
         <v>54</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.01547120591695468</v>
       </c>
@@ -1767,9 +1755,6 @@
       <c r="O8" t="n">
         <v>50</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.01432519066384693</v>
       </c>
@@ -2310,9 +2295,6 @@
       <c r="O11" t="n">
         <v>52</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.0148981982904008</v>
       </c>
@@ -2463,9 +2445,6 @@
       <c r="O12" t="n">
         <v>41</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.01174665634435448</v>
       </c>
@@ -2616,9 +2595,6 @@
       <c r="O13" t="n">
         <v>24</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.006876091518646525</v>
       </c>
@@ -2769,9 +2745,6 @@
       <c r="O14" t="n">
         <v>51</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01461169447712387</v>
       </c>
@@ -3312,9 +3285,6 @@
       <c r="O17" t="n">
         <v>43</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.01231966397090836</v>
       </c>
@@ -3465,9 +3435,6 @@
       <c r="O18" t="n">
         <v>22</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.006303083892092647</v>
       </c>
@@ -3618,9 +3585,6 @@
       <c r="O19" t="n">
         <v>33</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.009454625838138971</v>
       </c>
@@ -3771,9 +3735,6 @@
       <c r="O20" t="n">
         <v>46</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.01317917541073917</v>
       </c>
@@ -4314,9 +4275,6 @@
       <c r="O23" t="n">
         <v>36</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.01031413727796979</v>
       </c>
@@ -4467,9 +4425,6 @@
       <c r="O24" t="n">
         <v>35</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.01002763346469285</v>
       </c>
@@ -4620,9 +4575,6 @@
       <c r="O25" t="n">
         <v>34</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.00974112965141591</v>
       </c>
@@ -4773,9 +4725,6 @@
       <c r="O26" t="n">
         <v>50</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.01432519066384693</v>
       </c>
@@ -5316,9 +5265,6 @@
       <c r="O29" t="n">
         <v>52</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.0148981982904008</v>
       </c>
@@ -5469,9 +5415,6 @@
       <c r="O30" t="n">
         <v>36</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.01031413727796979</v>
       </c>
@@ -5622,9 +5565,6 @@
       <c r="O31" t="n">
         <v>25</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.007162595331923463</v>
       </c>
@@ -5775,9 +5715,6 @@
       <c r="O32" t="n">
         <v>14</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -9871,6 +9808,156 @@
         </is>
       </c>
       <c r="BC57" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>63</v>
+      </c>
+      <c r="O58" t="n">
+        <v>63</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.01804974023644713</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -9909,7 +9996,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -9992,7 +10079,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -10002,7 +10089,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -10054,7 +10141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1637</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d101/2026-2029.xlsx
+++ b/diseases/d101/2026-2029.xlsx
@@ -897,14 +897,12 @@
       <c r="O3" t="n">
         <v>13</v>
       </c>
+      <c r="P3" t="n">
+        <v>13</v>
+      </c>
       <c r="R3" t="n">
         <v>0.003724549572600201</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -917,23 +915,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1188,14 +1176,12 @@
       <c r="O5" t="n">
         <v>32</v>
       </c>
+      <c r="P5" t="n">
+        <v>32</v>
+      </c>
       <c r="R5" t="n">
         <v>0.009168122024862033</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1208,23 +1194,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1338,14 +1314,12 @@
       <c r="O6" t="n">
         <v>49</v>
       </c>
+      <c r="P6" t="n">
+        <v>49</v>
+      </c>
       <c r="R6" t="n">
         <v>0.01403868685056999</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1358,23 +1332,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1488,14 +1452,12 @@
       <c r="O7" t="n">
         <v>54</v>
       </c>
+      <c r="P7" t="n">
+        <v>54</v>
+      </c>
       <c r="R7" t="n">
         <v>0.01547120591695468</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1508,23 +1470,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1638,14 +1590,12 @@
       <c r="O8" t="n">
         <v>50</v>
       </c>
+      <c r="P8" t="n">
+        <v>50</v>
+      </c>
       <c r="R8" t="n">
         <v>0.01432519066384693</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1658,23 +1608,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2061,14 +2001,12 @@
       <c r="O11" t="n">
         <v>52</v>
       </c>
+      <c r="P11" t="n">
+        <v>52</v>
+      </c>
       <c r="R11" t="n">
         <v>0.0148981982904008</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2081,23 +2019,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2211,14 +2139,12 @@
       <c r="O12" t="n">
         <v>41</v>
       </c>
+      <c r="P12" t="n">
+        <v>41</v>
+      </c>
       <c r="R12" t="n">
         <v>0.01174665634435448</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2231,23 +2157,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2361,14 +2277,12 @@
       <c r="O13" t="n">
         <v>24</v>
       </c>
+      <c r="P13" t="n">
+        <v>24</v>
+      </c>
       <c r="R13" t="n">
         <v>0.006876091518646525</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2381,23 +2295,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2511,14 +2415,12 @@
       <c r="O14" t="n">
         <v>51</v>
       </c>
+      <c r="P14" t="n">
+        <v>51</v>
+      </c>
       <c r="R14" t="n">
         <v>0.01461169447712387</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2531,23 +2433,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2793,14 +2685,12 @@
       <c r="O16" t="n">
         <v>43</v>
       </c>
+      <c r="P16" t="n">
+        <v>43</v>
+      </c>
       <c r="R16" t="n">
         <v>0.01231966397090836</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2813,23 +2703,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3084,14 +2964,12 @@
       <c r="O18" t="n">
         <v>22</v>
       </c>
+      <c r="P18" t="n">
+        <v>22</v>
+      </c>
       <c r="R18" t="n">
         <v>0.006303083892092647</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3104,23 +2982,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3234,14 +3102,12 @@
       <c r="O19" t="n">
         <v>33</v>
       </c>
+      <c r="P19" t="n">
+        <v>33</v>
+      </c>
       <c r="R19" t="n">
         <v>0.009454625838138971</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3254,23 +3120,13 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3384,14 +3240,12 @@
       <c r="O20" t="n">
         <v>46</v>
       </c>
+      <c r="P20" t="n">
+        <v>46</v>
+      </c>
       <c r="R20" t="n">
         <v>0.01317917541073917</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3404,23 +3258,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3666,14 +3510,12 @@
       <c r="O22" t="n">
         <v>36</v>
       </c>
+      <c r="P22" t="n">
+        <v>36</v>
+      </c>
       <c r="R22" t="n">
         <v>0.01031413727796979</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3686,23 +3528,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3816,14 +3648,12 @@
       <c r="O23" t="n">
         <v>35</v>
       </c>
+      <c r="P23" t="n">
+        <v>35</v>
+      </c>
       <c r="R23" t="n">
         <v>0.01002763346469285</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3836,23 +3666,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4389,14 +4209,12 @@
       <c r="O27" t="n">
         <v>34</v>
       </c>
+      <c r="P27" t="n">
+        <v>34</v>
+      </c>
       <c r="R27" t="n">
         <v>0.00974112965141591</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4409,23 +4227,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4680,14 +4488,12 @@
       <c r="O29" t="n">
         <v>50</v>
       </c>
+      <c r="P29" t="n">
+        <v>50</v>
+      </c>
       <c r="R29" t="n">
         <v>0.01432519066384693</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4700,23 +4506,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5103,14 +4899,12 @@
       <c r="O32" t="n">
         <v>52</v>
       </c>
+      <c r="P32" t="n">
+        <v>52</v>
+      </c>
       <c r="R32" t="n">
         <v>0.0148981982904008</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5123,23 +4917,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5253,14 +5037,12 @@
       <c r="O33" t="n">
         <v>36</v>
       </c>
+      <c r="P33" t="n">
+        <v>36</v>
+      </c>
       <c r="R33" t="n">
         <v>0.01031413727796979</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5273,23 +5055,13 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5403,14 +5175,12 @@
       <c r="O34" t="n">
         <v>25</v>
       </c>
+      <c r="P34" t="n">
+        <v>25</v>
+      </c>
       <c r="R34" t="n">
         <v>0.007162595331923463</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5423,23 +5193,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5694,14 +5454,12 @@
       <c r="O36" t="n">
         <v>14</v>
       </c>
+      <c r="P36" t="n">
+        <v>14</v>
+      </c>
       <c r="R36" t="n">
         <v>0.00401105338587714</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5714,23 +5472,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5844,14 +5592,12 @@
       <c r="O37" t="n">
         <v>17</v>
       </c>
+      <c r="P37" t="n">
+        <v>17</v>
+      </c>
       <c r="R37" t="n">
         <v>0.004870564825707955</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5864,23 +5610,13 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6126,14 +5862,12 @@
       <c r="O39" t="n">
         <v>42</v>
       </c>
+      <c r="P39" t="n">
+        <v>42</v>
+      </c>
       <c r="R39" t="n">
         <v>0.01203316015763142</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6146,23 +5880,13 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6276,14 +6000,12 @@
       <c r="O40" t="n">
         <v>49</v>
       </c>
+      <c r="P40" t="n">
+        <v>49</v>
+      </c>
       <c r="R40" t="n">
         <v>0.01403868685056999</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6296,23 +6018,13 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6426,14 +6138,12 @@
       <c r="O41" t="n">
         <v>56</v>
       </c>
+      <c r="P41" t="n">
+        <v>56</v>
+      </c>
       <c r="R41" t="n">
         <v>0.01604421354350856</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6446,23 +6156,13 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6717,14 +6417,12 @@
       <c r="O43" t="n">
         <v>18</v>
       </c>
+      <c r="P43" t="n">
+        <v>18</v>
+      </c>
       <c r="R43" t="n">
         <v>0.005157068638984894</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6737,23 +6435,13 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6999,14 +6687,12 @@
       <c r="O45" t="n">
         <v>28</v>
       </c>
+      <c r="P45" t="n">
+        <v>28</v>
+      </c>
       <c r="R45" t="n">
         <v>0.00802210677175428</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7019,23 +6705,13 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7149,14 +6825,12 @@
       <c r="O46" t="n">
         <v>45</v>
       </c>
+      <c r="P46" t="n">
+        <v>45</v>
+      </c>
       <c r="R46" t="n">
         <v>0.01289267159746223</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7169,23 +6843,13 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7440,14 +7104,12 @@
       <c r="O48" t="n">
         <v>34</v>
       </c>
+      <c r="P48" t="n">
+        <v>34</v>
+      </c>
       <c r="R48" t="n">
         <v>0.00974112965141591</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7460,23 +7122,13 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7590,14 +7242,12 @@
       <c r="O49" t="n">
         <v>35</v>
       </c>
+      <c r="P49" t="n">
+        <v>35</v>
+      </c>
       <c r="R49" t="n">
         <v>0.01002763346469285</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7610,23 +7260,13 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7872,14 +7512,12 @@
       <c r="O51" t="n">
         <v>28</v>
       </c>
+      <c r="P51" t="n">
+        <v>28</v>
+      </c>
       <c r="R51" t="n">
         <v>0.00802210677175428</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7892,23 +7530,13 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8448,14 +8076,12 @@
       <c r="O55" t="n">
         <v>51</v>
       </c>
+      <c r="P55" t="n">
+        <v>51</v>
+      </c>
       <c r="R55" t="n">
         <v>0.01461169447712387</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8468,23 +8094,13 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8598,14 +8214,12 @@
       <c r="O56" t="n">
         <v>27</v>
       </c>
+      <c r="P56" t="n">
+        <v>27</v>
+      </c>
       <c r="R56" t="n">
         <v>0.007735602958477341</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8618,23 +8232,13 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8748,14 +8352,12 @@
       <c r="O57" t="n">
         <v>80</v>
       </c>
+      <c r="P57" t="n">
+        <v>80</v>
+      </c>
       <c r="R57" t="n">
         <v>0.02292030506215508</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8768,23 +8370,13 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9183,14 +8775,12 @@
       <c r="O60" t="n">
         <v>82</v>
       </c>
+      <c r="P60" t="n">
+        <v>82</v>
+      </c>
       <c r="R60" t="n">
         <v>0.02349331268870896</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9203,23 +8793,13 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9333,14 +8913,12 @@
       <c r="O61" t="n">
         <v>45</v>
       </c>
+      <c r="P61" t="n">
+        <v>45</v>
+      </c>
       <c r="R61" t="n">
         <v>0.01289267159746223</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9353,23 +8931,13 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9768,14 +9336,12 @@
       <c r="O64" t="n">
         <v>63</v>
       </c>
+      <c r="P64" t="n">
+        <v>63</v>
+      </c>
       <c r="R64" t="n">
         <v>0.01804974023644713</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9788,23 +9354,13 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9918,14 +9474,12 @@
       <c r="O65" t="n">
         <v>60</v>
       </c>
+      <c r="P65" t="n">
+        <v>60</v>
+      </c>
       <c r="R65" t="n">
         <v>0.01719022879661631</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9938,23 +9492,13 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10353,14 +9897,12 @@
       <c r="O68" t="n">
         <v>35</v>
       </c>
+      <c r="P68" t="n">
+        <v>35</v>
+      </c>
       <c r="R68" t="n">
         <v>0.01002763346469285</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10373,23 +9915,13 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10503,14 +10035,12 @@
       <c r="O69" t="n">
         <v>50</v>
       </c>
+      <c r="P69" t="n">
+        <v>50</v>
+      </c>
       <c r="R69" t="n">
         <v>0.01432519066384693</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10523,23 +10053,13 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10653,14 +10173,12 @@
       <c r="O70" t="n">
         <v>63</v>
       </c>
+      <c r="P70" t="n">
+        <v>63</v>
+      </c>
       <c r="R70" t="n">
         <v>0.01804974023644713</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10673,23 +10191,13 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10726,6 +10234,144 @@
         </is>
       </c>
       <c r="BC70" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>63</v>
+      </c>
+      <c r="O71" t="n">
+        <v>63</v>
+      </c>
+      <c r="P71" t="n">
+        <v>63</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.01804974023644713</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -10764,7 +10410,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10493,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -10857,7 +10503,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -10909,7 +10555,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1723</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d101/2026-2029.xlsx
+++ b/diseases/d101/2026-2029.xlsx
@@ -10267,111 +10267,255 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>耳念珠菌感染</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b0964fed61e9f66d5bc3d43c4e28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b0964fed61e9f66d5bc3d43c4e28</t>
+        </is>
+      </c>
+      <c r="AT71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>candida-auris-infection</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>D101</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Candida auris infection</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Candida auris infection</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>耳念珠菌感染</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>Fungal</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N71" t="n">
+      <c r="N72" t="n">
         <v>63</v>
       </c>
-      <c r="O71" t="n">
+      <c r="O72" t="n">
         <v>63</v>
       </c>
-      <c r="P71" t="n">
+      <c r="P72" t="n">
         <v>63</v>
       </c>
-      <c r="R71" t="n">
+      <c r="R72" t="n">
         <v>0.01804974023644713</v>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AO71" t="inlineStr">
+      <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP71" t="inlineStr">
+      <c r="AP72" t="inlineStr">
         <is>
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS71" t="inlineStr"/>
-      <c r="AT71" t="n">
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
         <v>0</v>
       </c>
-      <c r="AV71" t="inlineStr">
+      <c r="AV72" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW71" t="inlineStr">
+      <c r="AW72" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
+      <c r="AX72" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr">
+      <c r="AY72" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
+      <c r="AZ72" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA71" t="inlineStr">
+      <c r="BA72" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB71" t="inlineStr">
+      <c r="BB72" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC71" t="inlineStr">
+      <c r="BC72" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -10493,7 +10637,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -10503,7 +10647,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -10555,7 +10699,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="16">
